--- a/KLMPaletas.xlsx
+++ b/KLMPaletas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alelo\Documents\interfaces\auraweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC143292-C36A-4A1B-8C08-8BFC8DD69A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D29457C-5996-4BDD-A2C8-1D30E227F94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4990" yWindow="530" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paletas" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="48">
   <si>
     <t>Inner</t>
   </si>
@@ -128,12 +128,6 @@
     <t>Complete Purchase</t>
   </si>
   <si>
-    <t>Elegir Color Primario</t>
-  </si>
-  <si>
-    <t>Elegir Color Secundario</t>
-  </si>
-  <si>
     <t>Apuntar + Create Tema</t>
   </si>
   <si>
@@ -171,13 +165,28 @@
   </si>
   <si>
     <t>Pagar con otro método</t>
+  </si>
+  <si>
+    <t>Elegir Color 1</t>
+  </si>
+  <si>
+    <t>Elegir Color 2</t>
+  </si>
+  <si>
+    <t>Elegir Color 3</t>
+  </si>
+  <si>
+    <t>Elegir Color 4</t>
+  </si>
+  <si>
+    <t>Elegir Color 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +197,11 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -553,7 +567,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -572,7 +586,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2">
@@ -597,7 +611,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2">
@@ -621,150 +635,173 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
-        <f ca="1">SUM(C3:C27)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2">
-        <f ca="1">SUM(D3:D27)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2">
-        <f ca="1">SUM(E3:E27)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <f ca="1">SUM(F3:F27)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
-        <f ca="1">SUM(G3:G27)</f>
-        <v>3</v>
-      </c>
-      <c r="H7" s="2">
-        <f ca="1">SUM(H3:H27)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <f ca="1">SUM(I3:I27)</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <f ca="1">SUM(J3:J27)</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <f ca="1">SUM(K3:K27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
-        <f ca="1">C1*C7</f>
-        <v>2.4000000000000004</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2">
-        <f ca="1">D1*D7</f>
-        <v>3.3000000000000003</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
-        <f ca="1">E1*E7</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <f ca="1">F1*F7</f>
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2">
-        <f ca="1">G1*G7</f>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="H8" s="2">
-        <f ca="1">H1*H7</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <f ca="1">I1*I7</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <f ca="1">J1*J7</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <f ca="1">K1*K7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2">
+        <f>SUM(C3:C8)</f>
+        <v>30</v>
+      </c>
+      <c r="D10" s="2">
+        <f>SUM(D3:D8)</f>
+        <v>6</v>
+      </c>
+      <c r="E10" s="2">
+        <f>SUM(E3:E8)</f>
+        <v>5</v>
+      </c>
+      <c r="F10" s="2">
+        <f>SUM(F3:F8)</f>
+        <v>5</v>
+      </c>
+      <c r="G10" s="2">
+        <f>SUM(G3:G8)</f>
+        <v>6</v>
+      </c>
+      <c r="H10" s="2">
+        <f ca="1">SUM(H3:H27)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <f ca="1">SUM(I3:I27)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <f ca="1">SUM(J3:J27)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <f ca="1">SUM(K3:K27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2">
+        <f>C1*C10</f>
+        <v>6</v>
+      </c>
+      <c r="D11" s="2">
+        <f>D1*D10</f>
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="E11" s="2">
+        <f>E1*E10</f>
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <f>F1*F10</f>
+        <v>6</v>
+      </c>
+      <c r="G11" s="2">
+        <f>G1*G10</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="H11" s="2">
+        <f ca="1">H1*H10</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <f ca="1">I1*I10</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <f ca="1">J1*J10</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <f ca="1">K1*K10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2">
-        <f ca="1">SUM(C8:K8)</f>
-        <v>9.2000000000000011</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2">
+        <v>15.2</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -865,6 +902,7 @@
       <c r="K19" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0"/>
 </worksheet>
@@ -950,7 +988,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2">
@@ -1000,7 +1038,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2">
@@ -1025,7 +1063,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -1075,7 +1113,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1259,7 +1297,7 @@
         <v>6</v>
       </c>
       <c r="H29" s="2">
-        <f t="shared" ref="C29:K29" si="0">SUM(H3:H27)</f>
+        <f t="shared" ref="H29:K29" si="0">SUM(H3:H27)</f>
         <v>0</v>
       </c>
       <c r="I29" s="2">
@@ -1421,7 +1459,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1872,7 +1910,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1891,7 +1929,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1910,7 +1948,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1929,7 +1967,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1967,7 +2005,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2005,7 +2043,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7">
@@ -2030,7 +2068,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2049,7 +2087,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2196,7 +2234,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2215,7 +2253,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -2479,39 +2517,39 @@
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2">
-        <f>SUM(C3:C34)</f>
+        <f t="shared" ref="C36:K36" si="0">SUM(C3:C34)</f>
         <v>62</v>
       </c>
       <c r="D36" s="2">
-        <f>SUM(D3:D34)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="E36" s="2">
-        <f>SUM(E3:E34)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="F36" s="2">
-        <f>SUM(F3:F34)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="G36" s="2">
-        <f>SUM(G3:G34)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="H36" s="2">
-        <f>SUM(H3:H34)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I36" s="2">
-        <f>SUM(I3:I34)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J36" s="2">
-        <f>SUM(J3:J34)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K36" s="2">
-        <f>SUM(K3:K34)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2521,39 +2559,39 @@
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2">
-        <f>C1*C36</f>
+        <f t="shared" ref="C37:K37" si="1">C1*C36</f>
         <v>12.4</v>
       </c>
       <c r="D37" s="2">
-        <f>D1*D36</f>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="E37" s="2">
-        <f>E1*E36</f>
+        <f t="shared" si="1"/>
         <v>5.6000000000000005</v>
       </c>
       <c r="F37" s="2">
-        <f>F1*F36</f>
+        <f t="shared" si="1"/>
         <v>9.6</v>
       </c>
       <c r="G37" s="2">
-        <f>G1*G36</f>
+        <f t="shared" si="1"/>
         <v>3.1</v>
       </c>
       <c r="H37" s="2">
-        <f>H1*H36</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I37" s="2">
-        <f>I1*I36</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J37" s="2">
-        <f>J1*J36</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K37" s="2">
-        <f>K1*K36</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
